--- a/astro-site/public/dl/chocolate-shop-checklist-templates/06-chocolate-shop-seasonal-checklists.xlsx
+++ b/astro-site/public/dl/chocolate-shop-checklist-templates/06-chocolate-shop-seasonal-checklists.xlsx
@@ -627,9 +627,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Holiday Season, Valentine's Day, Easter, Mother's Day and more.</t>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>▸ Holiday Season, Valentine's Day and Easter (Mother's Day and the rest of the year: BONUS 02 calendar).</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Plan extra production: shifts, seasonal staff</t>
+          <t>Plan extra production: shifts and seasonal staff (minors: FLSA hour limits; under 16, no operating or cleaning the tempering or panning machine; check state work permits)</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Make artisan bark and toffee: praline, nut brittle, truffle</t>
+          <t>Make holiday bark, toffee and brittle: peppermint bark, chocolate-dipped English toffee, nut brittle</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Plan chocolate Easter basket production if applicable</t>
+          <t>Plan filled Easter basket orders and showpiece eggs, if you offer them</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Make decorated chocolate Easter baskets</t>
+          <t>Make large decorated and filled eggs and chocolate centerpieces; assemble filled Easter baskets</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
